--- a/results/breakdown/2020/nitrous oxide production, AON 90 membrane, fossil ammonia.xlsx
+++ b/results/breakdown/2020/nitrous oxide production, AON 90 membrane, fossil ammonia.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>3.165433565325343</v>
+        <v>3.16543356532534</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0006352359045057057</v>
+        <v>0.0006352359045057036</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -477,7 +477,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.05406783283407908</v>
+        <v>0.05406783283407911</v>
       </c>
       <c r="E5">
         <v>1</v>
